--- a/artfynd/A 10646-2024 artfynd.xlsx
+++ b/artfynd/A 10646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61299592</v>
+        <v>61798491</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691684.9368273357</v>
+        <v>691697</v>
       </c>
       <c r="R2" t="n">
-        <v>6627911.787990437</v>
+        <v>6627729</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -747,27 +742,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
+          <t>På rötskadad asplåga. Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,62 +773,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61299916</v>
+        <v>114785342</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>937</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eriksberg, NO om, Upl</t>
+          <t>Kundby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691784.1796991776</v>
+        <v>691579</v>
       </c>
       <c r="R3" t="n">
-        <v>6627801.769344756</v>
+        <v>6627649</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,27 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,56 +859,54 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61299871</v>
+        <v>61783408</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691766.8343892018</v>
+        <v>691580</v>
       </c>
       <c r="R4" t="n">
-        <v>6627883.184032428</v>
+        <v>6627799</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,27 +948,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga. Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
+          <t>På granlåga. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,60 +979,54 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61300070</v>
+        <v>67981680</v>
       </c>
       <c r="B5" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691712.1834204157</v>
+        <v>691711</v>
       </c>
       <c r="R5" t="n">
-        <v>6627873.804890744</v>
+        <v>6627912</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,27 +1053,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
+          <t>På gammal rötskadad granlåga. Medobservatör Ulf Birgersson Länsstyrelsen i Stockhom.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1155,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61299923</v>
+        <v>61300070</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,36 +1102,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691795.9674738622</v>
+        <v>691712</v>
       </c>
       <c r="R6" t="n">
-        <v>6627779.148192294</v>
+        <v>6627874</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,21 +1162,11 @@
           <t>2016-09-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-09-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
@@ -1256,7 +1178,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61783303</v>
+        <v>61798472</v>
       </c>
       <c r="B7" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,43 +1207,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691624.1248602554</v>
+        <v>691782</v>
       </c>
       <c r="R7" t="n">
-        <v>6627687.988986841</v>
+        <v>6627771</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,24 +1266,14 @@
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På höggstubbe av björk med fnösktickor.</t>
+          <t>Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,6 +1282,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1401,37 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61783408</v>
+        <v>61798477</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691579.9771595667</v>
+        <v>691765</v>
       </c>
       <c r="R8" t="n">
-        <v>6627798.829936677</v>
+        <v>6627781</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1476,24 +1371,14 @@
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
+          <t>Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,15 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61783339</v>
+        <v>61299923</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,21 +1417,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691573.8973753183</v>
+        <v>691796</v>
       </c>
       <c r="R9" t="n">
-        <v>6627799.022037445</v>
+        <v>6627779</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1593,27 +1473,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga vid grupp med barkborredödade granar.</t>
+          <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,22 +1504,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61783471</v>
+        <v>115909676</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,39 +1522,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eriksberg, NO om, Upl</t>
+          <t>Beateberg kalkbarrskog, Eriksberg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691762.8879773214</v>
+        <v>691680</v>
       </c>
       <c r="R10" t="n">
-        <v>6627891.059981991</v>
+        <v>6627854</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,27 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granlåga. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,78 +1590,65 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61783452</v>
+        <v>61299592</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691608.2481747756</v>
+        <v>691685</v>
       </c>
       <c r="R11" t="n">
-        <v>6627731.104543822</v>
+        <v>6627912</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1840,27 +1675,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På torrgran. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
+          <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,6 +1694,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1880,44 +1706,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61783433</v>
+        <v>61299871</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691589.7734197457</v>
+        <v>691767</v>
       </c>
       <c r="R12" t="n">
-        <v>6627755.907162937</v>
+        <v>6627883</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1959,27 +1780,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På torrgran. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
+          <t>På granlåga. Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,22 +1811,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>61783009</v>
+        <v>61783471</v>
       </c>
       <c r="B13" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,37 +1829,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219862</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691532.073555406</v>
+        <v>691763</v>
       </c>
       <c r="R13" t="n">
-        <v>6627835.246889696</v>
+        <v>6627891</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2083,24 +1888,14 @@
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka fynd.</t>
+          <t>På granlåga. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2109,6 +1904,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2127,15 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61798477</v>
+        <v>67982372</v>
       </c>
       <c r="B14" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4363</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2169,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691765.0118537792</v>
+        <v>691582</v>
       </c>
       <c r="R14" t="n">
-        <v>6627781.088330866</v>
+        <v>6627648</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2199,27 +1990,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
+          <t>På granlåga. Medobservatör Ulf Birgersson Länsstyrelsen i Stockhom.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2240,22 +2021,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>61798379</v>
+        <v>115910381</v>
       </c>
       <c r="B15" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,46 +2039,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Eriksberg, NO om, Upl</t>
+          <t>Kalkbarrskog Beateberg , Liestalund, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691757.938716424</v>
+        <v>691774</v>
       </c>
       <c r="R15" t="n">
-        <v>6627947.864132958</v>
+        <v>6627887</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2326,22 +2093,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,65 +2113,59 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>61798848</v>
+        <v>61299916</v>
       </c>
       <c r="B16" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691731.0227443295</v>
+        <v>691784</v>
       </c>
       <c r="R16" t="n">
-        <v>6627733.890515515</v>
+        <v>6627802</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2441,27 +2192,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Finns spridd inom området. Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
+          <t>Gammal naturskogsartad skog barrblandskog på delvis blockig mark. Död ved finns allmänt förekommande. Intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,6 +2211,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2481,22 +2223,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>61798491</v>
+        <v>67981724</v>
       </c>
       <c r="B17" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>366</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2530,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691696.8724559009</v>
+        <v>691772</v>
       </c>
       <c r="R17" t="n">
-        <v>6627729.102126498</v>
+        <v>6627772</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2560,27 +2297,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På rötskadad asplåga. Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
+          <t>Allmänt förekommande. Medobservatör Ulf Birgersson Länsstyrelsen i Stockhom.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,22 +2328,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kjell  Andersson, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>61798472</v>
+        <v>115909171</v>
       </c>
       <c r="B18" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,39 +2346,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eriksberg, NO om, Upl</t>
+          <t>Eriksberg, Eriksberg, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691782.2308496383</v>
+        <v>691735</v>
       </c>
       <c r="R18" t="n">
-        <v>6627770.866028499</v>
+        <v>6627713</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2680,27 +2405,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-10-03</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2709,74 +2429,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67981680</v>
+        <v>115949857</v>
       </c>
       <c r="B19" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eriksberg, NO om, Upl</t>
+          <t>Eriksberg, Eriksberg, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691711.2213394642</v>
+        <v>691666</v>
       </c>
       <c r="R19" t="n">
-        <v>6627912.131581818</v>
+        <v>6627727</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,27 +2512,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal rötskadad granlåga. Medobservatör Ulf Birgersson Länsstyrelsen i Stockhom.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,34 +2536,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67981724</v>
+        <v>61783452</v>
       </c>
       <c r="B20" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,36 +2565,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691772.0631556633</v>
+        <v>691608</v>
       </c>
       <c r="R20" t="n">
-        <v>6627771.857170576</v>
+        <v>6627731</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2920,27 +2628,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Allmänt förekommande. Medobservatör Ulf Birgersson Länsstyrelsen i Stockhom.</t>
+          <t>På torrgran. Gammal barrblandskog med inslag av gammal rötskadad asp. Delvis blockrika partier och död ved allmänt förekommande. Mycket intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2949,7 +2647,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2961,60 +2658,64 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115949857</v>
+        <v>115909941</v>
       </c>
       <c r="B21" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eriksberg (Eriksberg), Upl</t>
+          <t>Kalkbarrskog Beateberg , Liestalund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691666</v>
+        <v>691716</v>
       </c>
       <c r="R21" t="n">
-        <v>6627727</v>
+        <v>6627886</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3041,54 +2742,40 @@
           <t>2024-04-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-04-13</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115909815</v>
+        <v>61782988</v>
       </c>
       <c r="B22" t="n">
-        <v>96619</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,37 +2783,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>101735</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Liestalund (Liestalund), Upl</t>
+          <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691694</v>
+        <v>691565</v>
       </c>
       <c r="R22" t="n">
-        <v>6627869</v>
+        <v>6627865</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3150,22 +2846,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk med fnösktickor.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3180,70 +2871,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115909171</v>
+        <v>61783303</v>
       </c>
       <c r="B23" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eriksberg (Eriksberg), Upl</t>
+          <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691735</v>
+        <v>691624</v>
       </c>
       <c r="R23" t="n">
-        <v>6627713</v>
+        <v>6627688</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3267,22 +2957,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:06</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:06</t>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På höggstubbe av björk med fnösktickor.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,27 +2982,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115909676</v>
+        <v>61798379</v>
       </c>
       <c r="B24" t="n">
-        <v>90829</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,37 +3005,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5321</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Beateberg kalkbarrskog (Eriksberg), Upl</t>
+          <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691680</v>
+        <v>691758</v>
       </c>
       <c r="R24" t="n">
-        <v>6627854</v>
+        <v>6627948</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3379,12 +3068,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,27 +3088,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115910381</v>
+        <v>61783009</v>
       </c>
       <c r="B25" t="n">
-        <v>90386</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3427,37 +3111,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog Beateberg  (Liestalund), Upl</t>
+          <t>Eriksberg, NO om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691774</v>
+        <v>691532</v>
       </c>
       <c r="R25" t="n">
-        <v>6627887</v>
+        <v>6627835</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3481,12 +3168,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka fynd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3501,27 +3193,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115909941</v>
+        <v>115909815</v>
       </c>
       <c r="B26" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,46 +3216,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog Beateberg  (Liestalund), Upl</t>
+          <t>Liestalund, Liestalund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691716</v>
+        <v>691694</v>
       </c>
       <c r="R26" t="n">
-        <v>6627886</v>
+        <v>6627869</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3595,33 +3273,147 @@
           <t>2024-04-13</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-04-13</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>61798848</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eriksberg, NO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>691731</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6627734</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Finns spridd inom området. Gammal barrblandskog med delvis inslag av gamla lövträd, främst rötskadad asp. Marken delvis blockrik och kalkpåverkad med inslag av död ved. Mycket intressant kryptogamflora.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10646-2024 artfynd.xlsx
+++ b/artfynd/A 10646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798491</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61783408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981680</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61300070</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798472</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299923</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115909676</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299592</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299871</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61783471</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67982372</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115910381</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299916</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981724</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2444,6 +2529,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115909171</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2551,6 +2641,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115949857</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2662,6 +2757,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61783452</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2769,6 +2869,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115909941</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2880,6 +2985,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61782988</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2991,6 +3101,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61783303</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3097,6 +3212,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798379</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61783009</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3309,6 +3434,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115909815</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3414,8 +3544,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>